--- a/analysis/2.topic_analaysis/corex_topics_anchor5.xlsx
+++ b/analysis/2.topic_analaysis/corex_topics_anchor5.xlsx
@@ -94,7 +94,7 @@
     <t>overdose, health, patient, disease, treatment, mental, therapy, nurse, clinic, pandemic, loneliness, medicine, doctor, addiction, insurance, drug</t>
   </si>
   <si>
-    <t>business, entrepreneur, self-employment, business owner, self employed, client, customer, firm, owner, small business</t>
+    <t>business, entrepreneur, self employment, business owner, self employed, client, customer, firm, owner, small business</t>
   </si>
   <si>
     <t>soccer, hockey, athlete, league, tournament, game, score, sport</t>
@@ -106,49 +106,49 @@
     <t>police, policeman, crime, theft, criminal, gunshot, homicide</t>
   </si>
   <si>
-    <t>book, author, novel, book review, write, wrote, poem, poetry, fiction, non-fiction</t>
-  </si>
-  <si>
-    <t>housing (0.667); apartment (0.573); rent (0.418); tenant (0.305); affordable (0.223); landlord (0.202); city (0.129); building (0.127); neighborhood (0.126); resident (0.117); street (0.083); area (0.080); mortgage (0.080); park (0.077); property (0.074)</t>
-  </si>
-  <si>
-    <t>school (1.367); student (1.051); college (0.742); education (0.649); university (0.602); teacher (0.496); classroom (0.232); tuition (0.199); learning (0.149); curriculum (0.130); high school (0.128); graduate (0.059); high (0.058); public school (0.052); grade (0.051)</t>
-  </si>
-  <si>
-    <t>wage (1.221); labor (0.920); worker (0.791); union (0.692); employment (0.198); strike (0.108); bargaining (0.096); economic (0.082); economy (0.070); minimum wage (0.067); organizing (0.065); job (0.057); think article (0.049); diversity letter (0.049); editor hear (0.049)</t>
-  </si>
-  <si>
-    <t>election (1.789); democrat (1.789); republican (1.729); candidate (1.531); campaign (1.486); vote (1.322); party (1.078); poll (0.983); politics (0.757); primary (0.654); ballot (0.406); voter (0.400); rally (0.329); democratic (0.327); presidential (0.225)</t>
-  </si>
-  <si>
-    <t>war (0.515); military (0.453); army (0.237); soldier (0.206); troop (0.165); defense (0.118); minister (0.096); government (0.084); prime minister (0.082); europe (0.069); country (0.066); combat (0.061); parliament (0.060); european (0.058); foreign (0.057)</t>
-  </si>
-  <si>
-    <t>financial (0.430); debt (0.259); loan (0.237); interest (0.210); credit (0.190); income (0.150); tax (0.135); percent (0.116); rate (0.102); increase (0.095); pay (0.095); cost (0.095); billion (0.094); federal (0.090); million (0.088)</t>
-  </si>
-  <si>
-    <t>child (0.575); family (0.465); parent (0.436); marriage (0.135); mother (0.104); life (0.099); father (0.088); friend (0.085); wedding (0.083); sibling (0.082); home (0.077); old (0.067); kid (0.064); divorce (0.064); son (0.063)</t>
-  </si>
-  <si>
-    <t>film (1.122); movie (0.825); theater (0.692); music (0.688); art (0.627); artist (0.569); play (0.447); performance (0.383); gallery (0.211); exhibition (0.192); character (0.118); actor (0.113); culture (0.106); star (0.099); comedy (0.096)</t>
-  </si>
-  <si>
-    <t>pandemic (0.246); health (0.238); treatment (0.070); right (0.060); doctor (0.059); change (0.059); national (0.057); public (0.056); question (0.052); term (0.052); left (0.051); insurance (0.049); mental (0.049); disease (0.049); point (0.048)</t>
-  </si>
-  <si>
-    <t>business (0.956); owner (0.652); customer (0.437); small business (0.278); firm (0.264); business owner (0.172); client (0.134); entrepreneur (0.099); company (0.093); store (0.074); market (0.068); shop (0.066); sale (0.065); price (0.060); restaurant (0.060)</t>
-  </si>
-  <si>
-    <t>game (0.311); sport (0.250); league (0.120); soccer (0.091); athlete (0.084); tournament (0.075); room (0.066); score (0.051); foot (0.051); hockey (0.049); night (0.048); club (0.044); eye (0.042); bar (0.042); table (0.042)</t>
-  </si>
-  <si>
-    <t>church (0.566); catholic (0.385); religion (0.276); belief (0.162); faith (0.157); evangelical (0.142); black (0.100); racial (0.088); white (0.084); sermon (0.073); african (0.066); african american (0.060); christianity (0.057); worship (0.053); mosque (0.050)</t>
-  </si>
-  <si>
-    <t>police (2.034); criminal (0.717); crime (0.534); police officer (0.105); homicide (0.100); officer (0.089); policeman (0.059); arrested (0.047); violence (0.045); arrest (0.044); law (0.041); prison (0.040); killed (0.040); prosecutor (0.037); justice (0.036)</t>
-  </si>
-  <si>
-    <t>book (0.841); novel (0.531); author (0.393); wrote (0.282); fiction (0.262); write (0.209); poetry (0.149); book review (0.148); poem (0.114); story (0.089); world (0.081); self (0.075); writer (0.067); writing (0.067); read (0.058)</t>
+    <t>book, author, novel, book review, write, wrote, poem, poetry, fiction, non fiction</t>
+  </si>
+  <si>
+    <t>housing (0.668); apartment (0.573); rent (0.418); tenant (0.305); affordable (0.223); landlord (0.203); city (0.129); building (0.127); neighborhood (0.127); resident (0.118); street (0.082); area (0.080); mortgage (0.080); park (0.077); property (0.074)</t>
+  </si>
+  <si>
+    <t>school (1.369); student (1.056); college (0.743); education (0.646); university (0.600); teacher (0.497); classroom (0.233); tuition (0.200); learning (0.149); curriculum (0.130); high school (0.129); graduate (0.059); high (0.057); public school (0.052); grade (0.051)</t>
+  </si>
+  <si>
+    <t>wage (1.226); labor (0.955); worker (0.792); union (0.712); employment (0.198); strike (0.109); bargaining (0.097); organizing (0.068); minimum wage (0.067); job (0.054); think article (0.049); editor hear (0.049); diversity letter (0.049); publishing diversity (0.049); committed publishing (0.049)</t>
+  </si>
+  <si>
+    <t>election (1.793); democrat (1.788); republican (1.728); candidate (1.530); campaign (1.490); vote (1.323); party (1.078); poll (0.984); politics (0.755); primary (0.654); ballot (0.406); voter (0.400); rally (0.329); democratic (0.326); presidential (0.225)</t>
+  </si>
+  <si>
+    <t>war (0.509); military (0.469); army (0.237); soldier (0.206); troop (0.166); defense (0.117); minister (0.096); government (0.083); prime minister (0.083); europe (0.070); country (0.066); combat (0.062); parliament (0.060); european (0.059); foreign (0.058)</t>
+  </si>
+  <si>
+    <t>financial (0.434); debt (0.260); loan (0.236); interest (0.210); credit (0.189); income (0.150); tax (0.136); percent (0.117); rate (0.103); increase (0.095); cost (0.095); pay (0.094); billion (0.093); federal (0.089); economic (0.087)</t>
+  </si>
+  <si>
+    <t>child (0.583); family (0.473); parent (0.438); marriage (0.138); mother (0.104); life (0.099); father (0.089); friend (0.084); wedding (0.084); sibling (0.082); home (0.077); old (0.068); divorce (0.064); son (0.064); kid (0.064)</t>
+  </si>
+  <si>
+    <t>film (1.129); movie (0.826); theater (0.700); music (0.694); art (0.626); artist (0.569); play (0.447); performance (0.384); gallery (0.211); exhibition (0.193); character (0.117); actor (0.114); culture (0.106); star (0.099); comedy (0.097)</t>
+  </si>
+  <si>
+    <t>pandemic (0.251); health (0.247); treatment (0.072); doctor (0.062); change (0.059); right (0.058); national (0.056); public (0.055); term (0.052); disease (0.051); insurance (0.051); left (0.051); question (0.050); mental (0.049); since (0.047)</t>
+  </si>
+  <si>
+    <t>business (0.949); owner (0.654); customer (0.433); small business (0.277); firm (0.263); business owner (0.171); client (0.134); entrepreneur (0.098); company (0.093); store (0.074); market (0.069); shop (0.066); sale (0.065); price (0.060); restaurant (0.060)</t>
+  </si>
+  <si>
+    <t>game (0.315); sport (0.252); league (0.120); soccer (0.094); athlete (0.086); tournament (0.077); room (0.066); foot (0.052); score (0.052); hockey (0.050); night (0.047); club (0.044); red (0.042); bar (0.042); team (0.042)</t>
+  </si>
+  <si>
+    <t>church (0.343); religion (0.234); catholic (0.212); belief (0.212); faith (0.161); evangelical (0.098); black (0.095); racial (0.091); white (0.089); american (0.065); sermon (0.059); african (0.059); african american (0.053); social (0.049); worship (0.049)</t>
+  </si>
+  <si>
+    <t>police (2.026); criminal (0.715); crime (0.538); police officer (0.105); homicide (0.100); officer (0.089); policeman (0.059); arrested (0.047); violence (0.045); arrest (0.044); law (0.041); prison (0.040); killed (0.040); prosecutor (0.037); justice (0.036)</t>
+  </si>
+  <si>
+    <t>book (0.788); novel (0.535); wrote (0.272); fiction (0.263); write (0.214); poetry (0.153); book review (0.146); poem (0.119); author (0.094); story (0.091); world (0.080); self (0.073); writer (0.068); writing (0.068); man (0.059)</t>
   </si>
 </sst>
 </file>
